--- a/results/Int All Data 1.0/Linea_fi_explain.xlsx
+++ b/results/Int All Data 1.0/Linea_fi_explain.xlsx
@@ -1685,7 +1685,7 @@
         <v>-0.0002106961847408462</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.002517318877588011</v>
+        <v>-0.002420234884484591</v>
       </c>
       <c r="F3" t="n">
         <v>0.001044038275665454</v>
@@ -1694,13 +1694,13 @@
         <v>0.01944313287465381</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006678878607757602</v>
+        <v>0.006996253540517151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003297112176761207</v>
+        <v>0.00329173294061274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001366335118013583</v>
+        <v>0.001113218271490143</v>
       </c>
       <c r="K3" t="n">
         <v>0.0005990182394734844</v>
@@ -1712,10 +1712,10 @@
         <v>-0.0001458807960070741</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00112319246055195</v>
+        <v>4.311341670832983e-06</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.002433341573466232</v>
+        <v>-0.002126725113003617</v>
       </c>
       <c r="P3" t="n">
         <v>-0.001886346336162548</v>
@@ -1724,7 +1724,7 @@
         <v>0.006192934974482784</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001044274252277656</v>
+        <v>-0.001092687377613859</v>
       </c>
       <c r="S3" t="n">
         <v>0.008863099186138455</v>
@@ -1736,7 +1736,7 @@
         <v>0.004193080918874863</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003280974468315807</v>
+        <v>0.00329173294061274</v>
       </c>
       <c r="W3" t="n">
         <v>0.001528307600461438</v>
@@ -1751,7 +1751,7 @@
         <v>0.0003355467380608434</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.002388259951970354</v>
+        <v>-0.002958458983707847</v>
       </c>
       <c r="AB3" t="n">
         <v>0.0005124611699766602</v>
@@ -1760,13 +1760,13 @@
         <v>0.09171659069866889</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0004126637843170746</v>
+        <v>0.0001736729558658187</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004016196964854623</v>
+        <v>0.003542824183789538</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0007092257129821831</v>
+        <v>-0.0006823295322398492</v>
       </c>
       <c r="AG3" t="n">
         <v>-4.299433290156913e-05</v>
@@ -1778,10 +1778,10 @@
         <v>0.00293032481634954</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002748427273360489</v>
+        <v>0.001295352143362282</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0114900584229434</v>
+        <v>0.01249597558270671</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01867201262472853</v>
@@ -1790,7 +1790,7 @@
         <v>0.01896633059723443</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001045751685841847</v>
+        <v>-0.000427719897519847</v>
       </c>
       <c r="AO3" t="n">
         <v>0.08690813516944682</v>
@@ -1802,7 +1802,7 @@
         <v>0.01370907694091921</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.003090968347318315</v>
+        <v>0.003542824183789538</v>
       </c>
       <c r="AS3" t="n">
         <v>-0.0002250607615711863</v>
@@ -1817,7 +1817,7 @@
         <v>0.0003574467254118008</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001832685981164339</v>
+        <v>-0.0003082500059254922</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0001211314421962306</v>
@@ -1826,13 +1826,13 @@
         <v>0.07937414540674047</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.001629169033400374</v>
+        <v>-0.0008975929172088748</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.003575697161514986</v>
+        <v>0.002924809587550489</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.00158938794336686</v>
+        <v>0.0009976719670354982</v>
       </c>
       <c r="BC3" t="n">
         <v>0.000642225889272897</v>
@@ -1844,10 +1844,10 @@
         <v>0.00501160338579306</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0007852261952880057</v>
+        <v>0.0002526818165897816</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.001907911486891033</v>
+        <v>0.001901169510918286</v>
       </c>
       <c r="BH3" t="n">
         <v>0.02999905950223442</v>
@@ -1856,7 +1856,7 @@
         <v>0.1030828863961659</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001666650104084747</v>
+        <v>0.0001178977381191415</v>
       </c>
       <c r="BK3" t="n">
         <v>0.06279713818623206</v>
@@ -1868,7 +1868,7 @@
         <v>0.02085314610123452</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.002731157086205679</v>
+        <v>0.002924809587550489</v>
       </c>
       <c r="BO3" t="n">
         <v>0.018538291295561</v>
@@ -1883,7 +1883,7 @@
         <v>0.013958668910279</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.008659209851021615</v>
+        <v>0.006706547129128125</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0002547287772367235</v>
@@ -1892,28 +1892,28 @@
         <v>0.0279590028014433</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01979663032359597</v>
+        <v>0.02029064385023133</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0002778871161201591</v>
+        <v>0.0002866350658194483</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.019387551353407</v>
+        <v>0.01334128992253018</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.002560148125406549</v>
+        <v>0.00123147679673522</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.001258372977477554</v>
+        <v>0.00123147679673522</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0008208006215687346</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.01626321728699784</v>
+        <v>0.01401469657693867</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002549826382989348</v>
+        <v>0.00287283829432838</v>
       </c>
       <c r="CD3" t="n">
         <v>0.003410456675340069</v>
@@ -1922,7 +1922,7 @@
         <v>0.0002657217779819033</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.01318302832994098</v>
+        <v>0.0001921759234558151</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4411343032024838</v>
@@ -1934,7 +1934,7 @@
         <v>0.3936523545932075</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0002866350658194483</v>
+        <v>0.0002920114099054694</v>
       </c>
       <c r="CK3" t="n">
         <v>0.001718953827056093</v>
@@ -1949,7 +1949,7 @@
         <v>0.01118484223918118</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.02904571883023014</v>
+        <v>0.02922861285927802</v>
       </c>
       <c r="CP3" t="n">
         <v>0.0002921340522560145</v>
@@ -1958,13 +1958,13 @@
         <v>0.04550588469311359</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01904724096508329</v>
+        <v>0.02190361535991922</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.2654807745629994</v>
+        <v>0.2656097298567899</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0625824714562198</v>
+        <v>0.06068898033195944</v>
       </c>
       <c r="CU3" t="n">
         <v>0.005965142992211522</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0009393878785916873</v>
+        <v>0.0008049069748800172</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.004979587437053921</v>
+        <v>0.003806913956688135</v>
       </c>
       <c r="CZ3" t="n">
         <v>0.0007685772043276983</v>
@@ -1988,7 +1988,7 @@
         <v>3.669669779417073e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.02703578964078898</v>
+        <v>0.02757909249178413</v>
       </c>
       <c r="DC3" t="n">
         <v>0.3762118034662298</v>
@@ -2000,7 +2000,7 @@
         <v>0.08235484359851632</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2657497363704228</v>
+        <v>0.2656044969944141</v>
       </c>
       <c r="DG3" t="n">
         <v>0.009486864245432445</v>
@@ -2015,7 +2015,7 @@
         <v>0.0003092377899017983</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.01033958531774089</v>
+        <v>0.01019434594173228</v>
       </c>
       <c r="DL3" t="n">
         <v>-0.0001798479934227182</v>
@@ -2024,28 +2024,28 @@
         <v>0.00441682184003888</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.00240368627246405</v>
+        <v>0.00225306766030698</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.005358977122255555</v>
+        <v>0.005455803372927955</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.004075975092707409</v>
+        <v>0.003667153145423922</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-4.043894022424e-05</v>
+        <v>-4.581817637270613e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-8.885206556044522e-05</v>
+        <v>-4.581817637270613e-05</v>
       </c>
       <c r="DS3" t="n">
         <v>-0.0003742907247381366</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.01256964670312384</v>
+        <v>0.01249971663319377</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.01172378765773638</v>
+        <v>0.01129344876585903</v>
       </c>
       <c r="DV3" t="n">
         <v>0.0004209314495028793</v>
@@ -2054,7 +2054,7 @@
         <v>0.0006274756831126505</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.01130237553529217</v>
+        <v>0.01144761491130078</v>
       </c>
       <c r="DY3" t="n">
         <v>0.02142426291137997</v>
@@ -2066,7 +2066,7 @@
         <v>0.01260176221766614</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.006009833053654469</v>
+        <v>0.005455803372927955</v>
       </c>
       <c r="EC3" t="n">
         <v>0.01721206996207904</v>
@@ -2081,7 +2081,7 @@
         <v>-2.329410130445187e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.003788302062486456</v>
+        <v>0.004030367689167464</v>
       </c>
       <c r="EH3" t="n">
         <v>7.650428287883074e-06</v>
@@ -2090,19 +2090,19 @@
         <v>0.006738978244065334</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0009347584738679549</v>
+        <v>0.0008433114593440162</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0107393258848115</v>
+        <v>0.01053491491116975</v>
       </c>
       <c r="EL3" t="n">
         <v>-6.574824738311279e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0002815075533867861</v>
+        <v>0.0003299206787229902</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0003299206787229914</v>
+        <v>0.0003299206787229902</v>
       </c>
       <c r="EO3" t="n">
         <v>0.0002011480711522673</v>
@@ -2111,7 +2111,7 @@
         <v>3.095227281893487e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.00386243683728841</v>
+        <v>0.003695680516685934</v>
       </c>
       <c r="ER3" t="n">
         <v>0.0006425612803908521</v>
@@ -2120,7 +2120,7 @@
         <v>-6.526896165582996e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0007652748673702924</v>
+        <v>0.0008459634095972912</v>
       </c>
       <c r="EU3" t="n">
         <v>0.01797067143193139</v>
@@ -2132,7 +2132,7 @@
         <v>0.01664219931231032</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.01038429629901268</v>
+        <v>0.01053491491116975</v>
       </c>
       <c r="EY3" t="n">
         <v>0.003719222049984486</v>
@@ -2154,7 +2154,7 @@
         <v>0.001069930628875619</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006690088210560242</v>
+        <v>0.006687345400250269</v>
       </c>
       <c r="F4" t="n">
         <v>0.001765646811518008</v>
@@ -2163,13 +2163,13 @@
         <v>0.04098203526091104</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01003502663178936</v>
+        <v>0.00931628115715937</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01053682344580673</v>
+        <v>0.010538920821642</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009120629745963178</v>
+        <v>0.009140959239989758</v>
       </c>
       <c r="K4" t="n">
         <v>0.001756020362094775</v>
@@ -2181,10 +2181,10 @@
         <v>0.0008649594933071207</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004156847665925178</v>
+        <v>0.002058192124436249</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005841892638506447</v>
+        <v>0.0058037655580561</v>
       </c>
       <c r="P4" t="n">
         <v>0.00297958518927664</v>
@@ -2193,7 +2193,7 @@
         <v>0.02068822633468708</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002949372783128941</v>
+        <v>0.003075811096618137</v>
       </c>
       <c r="S4" t="n">
         <v>0.02331831646984329</v>
@@ -2205,7 +2205,7 @@
         <v>0.007436370562194915</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0105431966579973</v>
+        <v>0.010538920821642</v>
       </c>
       <c r="W4" t="n">
         <v>0.01879733635566966</v>
@@ -2220,7 +2220,7 @@
         <v>0.000970982402944624</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.006897058704276187</v>
+        <v>0.007572120719558991</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0008796126614801855</v>
@@ -2229,13 +2229,13 @@
         <v>0.07133953334501196</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004762335022738269</v>
+        <v>0.005183213379251676</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.008344476299943166</v>
+        <v>0.008399430960745118</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00568528720809394</v>
+        <v>0.005688236892499011</v>
       </c>
       <c r="AG4" t="n">
         <v>0.001985647827531239</v>
@@ -2247,10 +2247,10 @@
         <v>0.01106605833474923</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01004513023007699</v>
+        <v>0.00907334747091907</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01932986324246244</v>
+        <v>0.0185572014004559</v>
       </c>
       <c r="AL4" t="n">
         <v>0.04100777988917417</v>
@@ -2259,7 +2259,7 @@
         <v>0.02131425705688129</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.007739285211095665</v>
+        <v>0.005297725322677618</v>
       </c>
       <c r="AO4" t="n">
         <v>0.03853295861362004</v>
@@ -2271,7 +2271,7 @@
         <v>0.02542400359432655</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.008695370633635038</v>
+        <v>0.008399430960745118</v>
       </c>
       <c r="AS4" t="n">
         <v>0.003849475621768095</v>
@@ -2286,7 +2286,7 @@
         <v>0.001280248056280463</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.005666417908001689</v>
+        <v>0.004762614862813157</v>
       </c>
       <c r="AX4" t="n">
         <v>0.0002894306539789718</v>
@@ -2295,13 +2295,13 @@
         <v>0.08884831572966763</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004264933321205954</v>
+        <v>0.002202745881841324</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.006715779224881602</v>
+        <v>0.006610228958693625</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005059596881773461</v>
+        <v>0.005838730338353784</v>
       </c>
       <c r="BC4" t="n">
         <v>0.001902968704472631</v>
@@ -2313,10 +2313,10 @@
         <v>0.009618797541303825</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00360112093497847</v>
+        <v>0.003964191635188743</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003135094900380862</v>
+        <v>0.003136572310189205</v>
       </c>
       <c r="BH4" t="n">
         <v>0.04042167215482865</v>
@@ -2325,7 +2325,7 @@
         <v>0.06596362565201055</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.005087655543935156</v>
+        <v>0.003196201412783202</v>
       </c>
       <c r="BK4" t="n">
         <v>0.07705385240517205</v>
@@ -2337,7 +2337,7 @@
         <v>0.02211158565871286</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.006701650401340819</v>
+        <v>0.006610228958693625</v>
       </c>
       <c r="BO4" t="n">
         <v>0.03159667171596655</v>
@@ -2352,7 +2352,7 @@
         <v>0.02570432507468327</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01472926248075594</v>
+        <v>0.01481872365165719</v>
       </c>
       <c r="BT4" t="n">
         <v>0.001278264766034427</v>
@@ -2361,28 +2361,28 @@
         <v>0.03125360323152133</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02497844974473247</v>
+        <v>0.02453409854278239</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0004584446548405994</v>
+        <v>0.0004540528595318398</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.02094452636588606</v>
+        <v>0.01674943292843311</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004076528510803502</v>
+        <v>0.001082138790100406</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001064701880110424</v>
+        <v>0.001082138790100406</v>
       </c>
       <c r="CA4" t="n">
         <v>0.003583910435860274</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.03128388731045463</v>
+        <v>0.03176321713309984</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.00786282751999536</v>
+        <v>0.007645263325127047</v>
       </c>
       <c r="CD4" t="n">
         <v>0.01250570749490551</v>
@@ -2391,7 +2391,7 @@
         <v>0.006302906220987795</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.04071208592376239</v>
+        <v>0.002528955936372666</v>
       </c>
       <c r="CG4" t="n">
         <v>0.1105502597231705</v>
@@ -2403,7 +2403,7 @@
         <v>0.1163012667297744</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0004540528595318398</v>
+        <v>0.0004583603194293931</v>
       </c>
       <c r="CK4" t="n">
         <v>0.002682250630930874</v>
@@ -2418,7 +2418,7 @@
         <v>0.01947992690247486</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0396323828660792</v>
+        <v>0.0394907273035408</v>
       </c>
       <c r="CP4" t="n">
         <v>0.0007452332098028195</v>
@@ -2427,13 +2427,13 @@
         <v>0.03653198435752605</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.02910004111642251</v>
+        <v>0.03241309960858264</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.1421717593160756</v>
+        <v>0.1421041307551418</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.06787583006098744</v>
+        <v>0.06573419577831854</v>
       </c>
       <c r="CU4" t="n">
         <v>0.01219077712193782</v>
@@ -2445,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.008551642966262043</v>
+        <v>0.008639276529839004</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.01686942136340458</v>
+        <v>0.01759213412415112</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.001520364691545058</v>
@@ -2457,7 +2457,7 @@
         <v>0.0001793518650549309</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0280601000014536</v>
+        <v>0.02825713149017309</v>
       </c>
       <c r="DC4" t="n">
         <v>0.05543669683241857</v>
@@ -2469,7 +2469,7 @@
         <v>0.05042746845945512</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1420212046795381</v>
+        <v>0.1421018917251856</v>
       </c>
       <c r="DG4" t="n">
         <v>0.01503336818078589</v>
@@ -2484,7 +2484,7 @@
         <v>0.002151695088525721</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.02218060310699587</v>
+        <v>0.02224717836302289</v>
       </c>
       <c r="DL4" t="n">
         <v>0.0007820913303518233</v>
@@ -2493,28 +2493,28 @@
         <v>0.01236513513343592</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003406656027627423</v>
+        <v>0.003490928195214912</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.01706726826265625</v>
+        <v>0.01703620588744666</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0133979440502547</v>
+        <v>0.01345431249439396</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0007226628832496152</v>
+        <v>0.0007220834972716965</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0007318074209690995</v>
+        <v>0.0007220834972716965</v>
       </c>
       <c r="DS4" t="n">
         <v>0.002410470759490771</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.02714175415846594</v>
+        <v>0.02717630688442392</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.03269619034080776</v>
+        <v>0.03283274234527486</v>
       </c>
       <c r="DV4" t="n">
         <v>0.00125927579302212</v>
@@ -2523,7 +2523,7 @@
         <v>0.001640299224546473</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.02934582214976929</v>
+        <v>0.02928216495642059</v>
       </c>
       <c r="DY4" t="n">
         <v>0.03594755305995781</v>
@@ -2535,7 +2535,7 @@
         <v>0.02894661103859607</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0169541182889514</v>
+        <v>0.01703620588744666</v>
       </c>
       <c r="EC4" t="n">
         <v>0.0196353285886394</v>
@@ -2550,7 +2550,7 @@
         <v>0.0007137692808060967</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.01365725574601234</v>
+        <v>0.01356352462120561</v>
       </c>
       <c r="EH4" t="n">
         <v>0.001815288887444129</v>
@@ -2559,16 +2559,16 @@
         <v>0.01383344575841371</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.00326082667051117</v>
+        <v>0.003252480628953806</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.02324876425996374</v>
+        <v>0.0233686627860078</v>
       </c>
       <c r="EL4" t="n">
         <v>0.0001343789158638868</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.00104410302849405</v>
+        <v>0.001015489242798753</v>
       </c>
       <c r="EN4" t="n">
         <v>0.001015489242798753</v>
@@ -2580,7 +2580,7 @@
         <v>7.998003610284299e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01247917627382045</v>
+        <v>0.01251725744428727</v>
       </c>
       <c r="ER4" t="n">
         <v>0.001908439639369265</v>
@@ -2589,7 +2589,7 @@
         <v>0.0007254385279702013</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.003176328731836759</v>
+        <v>0.00316190765611456</v>
       </c>
       <c r="EU4" t="n">
         <v>0.04807912728957345</v>
@@ -2601,7 +2601,7 @@
         <v>0.03310069754975353</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.02346801264302488</v>
+        <v>0.0233686627860078</v>
       </c>
       <c r="EY4" t="n">
         <v>0.01043503380453372</v>
@@ -2632,7 +2632,7 @@
         <v>-0.04368983957219256</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01447014523937605</v>
+        <v>-0.01129639591178055</v>
       </c>
       <c r="I5" t="n">
         <v>-0.01299435028248588</v>
@@ -2662,7 +2662,7 @@
         <v>-0.01871657754010699</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0079074771382464</v>
+        <v>-0.00839160839160843</v>
       </c>
       <c r="S5" t="n">
         <v>-0.004519774011299449</v>
@@ -2719,7 +2719,7 @@
         <v>-0.01812834224598935</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.006132329209252318</v>
+        <v>-0.001669941060903713</v>
       </c>
       <c r="AL5" t="n">
         <v>-0.06117647058823532</v>
@@ -2755,7 +2755,7 @@
         <v>-0.001090909090909098</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.005484764542936249</v>
+        <v>-0.00796126949973106</v>
       </c>
       <c r="AX5" t="n">
         <v>-0.0002689618074233846</v>
@@ -2764,13 +2764,13 @@
         <v>0.005989304812834206</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01312533620225931</v>
+        <v>-0.005809575040344317</v>
       </c>
       <c r="BA5" t="n">
         <v>-0.007062146892655374</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.002205486820871461</v>
+        <v>-0.008122646584185078</v>
       </c>
       <c r="BC5" t="n">
         <v>-0.002528240989779507</v>
@@ -2782,7 +2782,7 @@
         <v>-0.0005232862375719848</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.004002254791431748</v>
+        <v>-0.004464766003227594</v>
       </c>
       <c r="BG5" t="n">
         <v>-0.001906779661016955</v>
@@ -2992,7 +2992,7 @@
         <v>-0.001569858712715899</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.0009144701452394211</v>
+        <v>-0.0004838709677419284</v>
       </c>
       <c r="DY5" t="n">
         <v>-0.001277013752455791</v>
@@ -3004,7 +3004,7 @@
         <v>-0.0005913978494623606</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.02165775401069524</v>
+        <v>-0.02171122994652411</v>
       </c>
       <c r="EC5" t="n">
         <v>-0.004590395480226006</v>
@@ -3031,7 +3031,7 @@
         <v>-0.003319209039548043</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.0006455083378160698</v>
+        <v>-0.002689618074233513</v>
       </c>
       <c r="EL5" t="n">
         <v>-0.0003382187147688453</v>
@@ -3070,7 +3070,7 @@
         <v>-0.004114994363021396</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.004195804195804231</v>
+        <v>-0.002689618074233513</v>
       </c>
       <c r="EY5" t="n">
         <v>-0.008060879368658347</v>
@@ -3092,7 +3092,7 @@
         <v>-0.0006618012586598999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002403007115049038</v>
+        <v>-0.002255078120966181</v>
       </c>
       <c r="F6" t="n">
         <v>-4.155124653737741e-05</v>
@@ -3104,10 +3104,10 @@
         <v>0.003292644566882808</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0008463675441985092</v>
+        <v>-0.0008492950196534566</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.00258620814616064</v>
+        <v>-0.002560043834282044</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>-0.000787141429998589</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002805020544427344</v>
+        <v>-0.001673802892023255</v>
       </c>
       <c r="P6" t="n">
         <v>-0.003878093060785401</v>
@@ -3143,7 +3143,7 @@
         <v>-0.00016129032258064</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0008761912003957901</v>
+        <v>-0.0008492950196534566</v>
       </c>
       <c r="W6" t="n">
         <v>-0.002377062346195327</v>
@@ -3170,10 +3170,10 @@
         <v>-0.002267200803850025</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0003578060246046094</v>
+        <v>0.0001737273715295612</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0001886391996282405</v>
+        <v>1.308215593926465e-05</v>
       </c>
       <c r="AG6" t="n">
         <v>5.379236148465582e-05</v>
@@ -3188,7 +3188,7 @@
         <v>-0.0005465185974493109</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0008727762597213972</v>
+        <v>0.004241636864566342</v>
       </c>
       <c r="AL6" t="n">
         <v>0.004345581671956667</v>
@@ -3197,7 +3197,7 @@
         <v>0.00731068931068928</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.003835994056637318</v>
+        <v>-0.003953733460091017</v>
       </c>
       <c r="AO6" t="n">
         <v>0.05792910907746083</v>
@@ -3209,7 +3209,7 @@
         <v>0.001928355577940108</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.001469968691518353</v>
+        <v>0.0001737273715295612</v>
       </c>
       <c r="AS6" t="n">
         <v>0.000101803374054682</v>
@@ -3224,7 +3224,7 @@
         <v>-0.0004303244315651406</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001582600195503431</v>
+        <v>-0.00392764169314336</v>
       </c>
       <c r="AX6" t="n">
         <v>-8.021390374332582e-05</v>
@@ -3251,10 +3251,10 @@
         <v>0.0006928239979968276</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.000466295609152767</v>
+        <v>-0.002705196004364957</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.33689839572182e-05</v>
+        <v>5.355504224281715e-05</v>
       </c>
       <c r="BH6" t="n">
         <v>0.005340813033120673</v>
@@ -3263,7 +3263,7 @@
         <v>0.0755146373174627</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0002822580645161305</v>
+        <v>-0.001788545408272477</v>
       </c>
       <c r="BK6" t="n">
         <v>0.003620325824902485</v>
@@ -3275,7 +3275,7 @@
         <v>0.003788202725276552</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001310336746523849</v>
+        <v>-0.0008864529380246454</v>
       </c>
       <c r="BO6" t="n">
         <v>0.002597116174781941</v>
@@ -3290,7 +3290,7 @@
         <v>-0.001312447200704908</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.395633045463701e-05</v>
+        <v>-0.001390667432203707</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.00037627220976367</v>
@@ -3299,28 +3299,28 @@
         <v>0.0029766542728902</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0006714302974270586</v>
+        <v>0.003562003607252437</v>
       </c>
       <c r="BW6" t="n">
         <v>1.227897838899927e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.003985131273441675</v>
+        <v>-0.00148747372470362</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.001079624837693832</v>
+        <v>0.0006247415588074484</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0008264629143749536</v>
+        <v>0.0006247415588074484</v>
       </c>
       <c r="CA6" t="n">
         <v>-0.001321179501949193</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0002272727272727204</v>
+        <v>-0.00154715127701375</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001192150909301035</v>
+        <v>-0.0003764674239787686</v>
       </c>
       <c r="CD6" t="n">
         <v>-0.001962939810680484</v>
@@ -3329,7 +3329,7 @@
         <v>-0.002771347699919166</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0005222530232430439</v>
+        <v>-0.0009119745426632463</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3679984584950122</v>
@@ -3356,7 +3356,7 @@
         <v>4.275822196129764e-05</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.001107399951422924</v>
+        <v>0.002479105169282014</v>
       </c>
       <c r="CP6" t="n">
         <v>-3.33066907387547e-17</v>
@@ -3368,7 +3368,7 @@
         <v>0.001262309119451965</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.1729437869822485</v>
+        <v>0.1732530930607854</v>
       </c>
       <c r="CT6" t="n">
         <v>0.008844778108025027</v>
@@ -3386,7 +3386,7 @@
         <v>-0.0005422219514978899</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.001548952193844139</v>
+        <v>-0.002171297338642309</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.385041551244248e-05</v>
@@ -3407,7 +3407,7 @@
         <v>0.04108467603140521</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.1736161915008069</v>
+        <v>0.1732530930607854</v>
       </c>
       <c r="DG6" t="n">
         <v>-0.002103386809269178</v>
@@ -3431,10 +3431,10 @@
         <v>-0.0002007720786001477</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.000203606748109364</v>
+        <v>-7.84929356358044e-05</v>
       </c>
       <c r="DO6" t="n">
-        <v>0</v>
+        <v>6.139489194499914e-05</v>
       </c>
       <c r="DP6" t="n">
         <v>-0.000169109357384406</v>
@@ -3443,13 +3443,13 @@
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0001209677419354738</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="n">
         <v>-0.000392670157068059</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.000147347740667983</v>
+        <v>2.689618074232791e-05</v>
       </c>
       <c r="DU6" t="n">
         <v>-0.0001745200698080263</v>
@@ -3461,7 +3461,7 @@
         <v>-0.0003026716872870955</v>
       </c>
       <c r="DX6" t="n">
-        <v>3.68369351670006e-05</v>
+        <v>0.0001686841621036772</v>
       </c>
       <c r="DY6" t="n">
         <v>0.001638397337724151</v>
@@ -3488,7 +3488,7 @@
         <v>-0.0001203208556149887</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0006818181818182111</v>
+        <v>0</v>
       </c>
       <c r="EH6" t="n">
         <v>-0.0005606187341990865</v>
@@ -3506,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0002578585461689431</v>
+        <v>-8.326672684688675e-18</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-8.326672684688675e-18</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>-9.57966764418311e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>-8.068854222700872e-05</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
         <v>-0.0003342964751883559</v>
@@ -3573,10 +3573,10 @@
         <v>0.008844919786096228</v>
       </c>
       <c r="I7" t="n">
-        <v>7.910641394800468e-05</v>
+        <v>5.806518411556328e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009521016617790867</v>
+        <v>-2.709862511352521e-05</v>
       </c>
       <c r="K7" t="n">
         <v>2.908667830133771e-05</v>
@@ -3639,7 +3639,7 @@
         <v>-0.0004371053654539381</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002855926653569102</v>
+        <v>0.001970452446906773</v>
       </c>
       <c r="AF7" t="n">
         <v>0.0004944863426072533</v>
@@ -3693,7 +3693,7 @@
         <v>-5.347593582889498e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001045891380581249</v>
+        <v>0.0003430056886277955</v>
       </c>
       <c r="AX7" t="n">
         <v>3.03030303030305e-05</v>
@@ -3705,7 +3705,7 @@
         <v>2.770083102493492e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.002587162158088624</v>
+        <v>0.001633863873682845</v>
       </c>
       <c r="BB7" t="n">
         <v>7.84929356357822e-05</v>
@@ -3720,10 +3720,10 @@
         <v>0.002183600713012474</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0009116223143372015</v>
+        <v>0.0008214194768816241</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0006294182008467597</v>
+        <v>0.0005688121402406987</v>
       </c>
       <c r="BH7" t="n">
         <v>0.009174406143954299</v>
@@ -3732,7 +3732,7 @@
         <v>0.0888358796541196</v>
       </c>
       <c r="BJ7" t="n">
-        <v>7.84929356357822e-05</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
         <v>0.03343851386708527</v>
@@ -3744,7 +3744,7 @@
         <v>0.007717642526964575</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001513368983957203</v>
+        <v>0.001633863873682845</v>
       </c>
       <c r="BO7" t="n">
         <v>0.008016042780748654</v>
@@ -3759,7 +3759,7 @@
         <v>0.006920902603530227</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.002840302715483889</v>
+        <v>0.001471511681595655</v>
       </c>
       <c r="BT7" t="n">
         <v>2.689618074233069e-05</v>
@@ -3771,13 +3771,13 @@
         <v>0.009358305720986781</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0001328283841321609</v>
+        <v>0.0001432428939476815</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01867951925654546</v>
+        <v>0.01624486803519061</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001347340371015704</v>
+        <v>0.001209458606414881</v>
       </c>
       <c r="BZ7" t="n">
         <v>0.001209458606414881</v>
@@ -3786,7 +3786,7 @@
         <v>0.0005817609379144661</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.002578762838063858</v>
+        <v>0.001003996003995961</v>
       </c>
       <c r="CC7" t="n">
         <v>0.001026316595198862</v>
@@ -3798,7 +3798,7 @@
         <v>0.0004652808585250634</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0002803967433566756</v>
+        <v>-8.880320437115177e-05</v>
       </c>
       <c r="CG7" t="n">
         <v>0.4882436751189498</v>
@@ -3855,7 +3855,7 @@
         <v>0.0002926215059179227</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0006820603219495069</v>
+        <v>-0.0003342566943674795</v>
       </c>
       <c r="CZ7" t="n">
         <v>0.0002702505195784244</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.02548608637848473</v>
+        <v>0.02820260063346053</v>
       </c>
       <c r="DC7" t="n">
         <v>0.3823650354229922</v>
@@ -3891,7 +3891,7 @@
         <v>5.232862375716962e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0002908667830133771</v>
+        <v>0.0001882732651963148</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -3900,13 +3900,13 @@
         <v>-2.908667830133771e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.001528019491820359</v>
+        <v>0.001262828469480748</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001378676754062647</v>
+        <v>0.001740018223534651</v>
       </c>
       <c r="DP7" t="n">
-        <v>8.726003490401313e-05</v>
+        <v>8.068854222698096e-05</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3918,10 +3918,10 @@
         <v>2.770083102493492e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.001579913299370284</v>
+        <v>0.00147116606957125</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0002995145466377636</v>
+        <v>7.849293563578774e-05</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>0.0003076135125091306</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0005708921677507805</v>
+        <v>0.0007235072619687421</v>
       </c>
       <c r="DY7" t="n">
         <v>0.003826543838812568</v>
@@ -3942,7 +3942,7 @@
         <v>0.0004395510385654944</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.003117434381458267</v>
+        <v>0.001740018223534651</v>
       </c>
       <c r="EC7" t="n">
         <v>0.009530898965288076</v>
@@ -3957,7 +3957,7 @@
         <v>8.064516129031584e-05</v>
       </c>
       <c r="EG7" t="n">
-        <v>0</v>
+        <v>8.726003490401313e-05</v>
       </c>
       <c r="EH7" t="n">
         <v>0.0001308215593930018</v>
@@ -3996,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>2.908667830133771e-05</v>
+        <v>0.0001634952804518697</v>
       </c>
       <c r="EU7" t="n">
         <v>5.551115123125783e-18</v>
@@ -4030,7 +4030,7 @@
         <v>0.0002229703070039057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003273379064106851</v>
+        <v>0.0003696152457567991</v>
       </c>
       <c r="F8" t="n">
         <v>0.001793914721803166</v>
@@ -4045,7 +4045,7 @@
         <v>0.003861869040964175</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002262244895802407</v>
+        <v>0.002092888611061516</v>
       </c>
       <c r="K8" t="n">
         <v>0.0008877005347593253</v>
@@ -4057,7 +4057,7 @@
         <v>0.0001328139238199411</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001171812170494158</v>
+        <v>0.0003030998407090674</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4105,10 +4105,10 @@
         <v>0.1418044047271781</v>
       </c>
       <c r="AD8" t="n">
-        <v>9.333198231556151e-05</v>
+        <v>0.003198105620587999</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.004638679682566324</v>
+        <v>0.003728137846854327</v>
       </c>
       <c r="AF8" t="n">
         <v>0.001505143165616576</v>
@@ -4123,7 +4123,7 @@
         <v>0.004497936537863465</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.009243157380254153</v>
+        <v>0.006407208176438944</v>
       </c>
       <c r="AK8" t="n">
         <v>0.01299911860992193</v>
@@ -4135,7 +4135,7 @@
         <v>0.0406885277666915</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0050816703116457</v>
+        <v>0.002864074511096826</v>
       </c>
       <c r="AO8" t="n">
         <v>0.1065242417369293</v>
@@ -4162,7 +4162,7 @@
         <v>0.0006198046216579961</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.00520914529139851</v>
+        <v>0.002049591313574897</v>
       </c>
       <c r="AX8" t="n">
         <v>0.000354974760269458</v>
@@ -4174,7 +4174,7 @@
         <v>0.0002568383996955304</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.006909792742948495</v>
+        <v>0.004624531943399159</v>
       </c>
       <c r="BB8" t="n">
         <v>0.0007337547795593425</v>
@@ -4201,7 +4201,7 @@
         <v>0.1035272346700918</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.003521049082614633</v>
+        <v>0.0005549635601558106</v>
       </c>
       <c r="BK8" t="n">
         <v>0.0937708545261671</v>
@@ -4228,7 +4228,7 @@
         <v>0.01854010695187167</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.01870925228617536</v>
+        <v>0.01533145434047353</v>
       </c>
       <c r="BT8" t="n">
         <v>0.0001727487205972045</v>
@@ -4240,13 +4240,13 @@
         <v>0.03144412730127013</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0004592428753192212</v>
+        <v>0.0004893463548747368</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.02157258600963197</v>
+        <v>0.02072167840074445</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.001798775228566479</v>
+        <v>0.001647058823529371</v>
       </c>
       <c r="BZ8" t="n">
         <v>0.001647058823529371</v>
@@ -4255,10 +4255,10 @@
         <v>0.003059665699870062</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.01921983145060065</v>
+        <v>0.01292374705339757</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003317012348257295</v>
+        <v>0.003331104794705999</v>
       </c>
       <c r="CD8" t="n">
         <v>0.006027670390551266</v>
@@ -4267,7 +4267,7 @@
         <v>0.00198411113710494</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003326159247818214</v>
+        <v>0.0008835764814988211</v>
       </c>
       <c r="CG8" t="n">
         <v>0.5277942915048134</v>
@@ -4303,13 +4303,13 @@
         <v>0.07596779250582045</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.03422117514780769</v>
+        <v>0.04932669927628471</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.3776394358264819</v>
+        <v>0.3776525179824211</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.1252028612768012</v>
+        <v>0.1110016778448485</v>
       </c>
       <c r="CU8" t="n">
         <v>0.004787125977829265</v>
@@ -4360,7 +4360,7 @@
         <v>0.0007095821421568311</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.01138465442745837</v>
+        <v>0.01107285274634538</v>
       </c>
       <c r="DL8" t="n">
         <v>0.0001709970042276743</v>
@@ -4375,10 +4375,10 @@
         <v>0.007399206625597734</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.003911067474463794</v>
+        <v>0.002215240186943532</v>
       </c>
       <c r="DQ8" t="n">
-        <v>5.707810782317191e-05</v>
+        <v>4.363001745200657e-05</v>
       </c>
       <c r="DR8" t="n">
         <v>4.363001745200657e-05</v>
@@ -4390,7 +4390,7 @@
         <v>0.01004145741518909</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.003988533797310142</v>
+        <v>0.002393487130190994</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
         <v>0.006968237058834765</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.008082203764494991</v>
+        <v>0.007399206625597734</v>
       </c>
       <c r="EC8" t="n">
         <v>0.0310519329381387</v>
@@ -4426,7 +4426,7 @@
         <v>0.0002550167141825849</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0007893129059919901</v>
+        <v>0.0008398195211381409</v>
       </c>
       <c r="EH8" t="n">
         <v>0.0003558297658020765</v>
@@ -4435,7 +4435,7 @@
         <v>0.005839572192513384</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.001351252597892069</v>
+        <v>0.0006653999889625283</v>
       </c>
       <c r="EK8" t="n">
         <v>0.006701996283875617</v>
@@ -4456,7 +4456,7 @@
         <v>6.633508565213608e-05</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.001009553071076696</v>
+        <v>0.0008398195211381409</v>
       </c>
       <c r="ER8" t="n">
         <v>3.924646781789388e-05</v>
@@ -4465,7 +4465,7 @@
         <v>0.0002406417112299275</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.000489977694536406</v>
+        <v>0.0006653999889625283</v>
       </c>
       <c r="EU8" t="n">
         <v>0.004173289010179828</v>
@@ -4526,7 +4526,7 @@
         <v>0.0004278074866309822</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01140398063474981</v>
+        <v>0.00459569517161137</v>
       </c>
       <c r="O9" t="n">
         <v>0.003094302554027495</v>
@@ -4604,7 +4604,7 @@
         <v>0.04403723094822572</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01748251748251746</v>
+        <v>0.00592797783933523</v>
       </c>
       <c r="AO9" t="n">
         <v>0.1646774193548387</v>
@@ -4631,7 +4631,7 @@
         <v>0.002559627690517719</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01344809037116725</v>
+        <v>0.006340895869691665</v>
       </c>
       <c r="AX9" t="n">
         <v>0.0006355932203389814</v>
@@ -4670,7 +4670,7 @@
         <v>0.2575268817204301</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.01317912856374392</v>
+        <v>0.005991855730075624</v>
       </c>
       <c r="BK9" t="n">
         <v>0.2382258064516129</v>
@@ -4706,16 +4706,16 @@
         <v>0.08813559322033898</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.06305991855730075</v>
+        <v>0.06294357184409541</v>
       </c>
       <c r="BW9" t="n">
         <v>0.001333333333333342</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.05836471221086603</v>
+        <v>0.04909831297265851</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01377084454007527</v>
+        <v>0.0035485747527632</v>
       </c>
       <c r="BZ9" t="n">
         <v>0.0035485747527632</v>
@@ -4736,7 +4736,7 @@
         <v>0.01348870056497172</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.1288327057557826</v>
+        <v>0.004224598930481271</v>
       </c>
       <c r="CG9" t="n">
         <v>0.5483516483516484</v>
